--- a/wolf/Excel/AIWayPoint_AI路点表.xlsx
+++ b/wolf/Excel/AIWayPoint_AI路点表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9015"/>
+    <workbookView windowHeight="17205"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="82">
   <si>
     <t>Int</t>
   </si>
@@ -62,142 +62,82 @@
     <t/>
   </si>
   <si>
-    <t>-7230|-1800|241</t>
-  </si>
-  <si>
-    <t>2|20|1</t>
-  </si>
-  <si>
-    <t>-7230|700|241</t>
-  </si>
-  <si>
-    <t>2|22|1</t>
-  </si>
-  <si>
-    <t>-6730|-2490|241</t>
-  </si>
-  <si>
-    <t>7|6|1</t>
-  </si>
-  <si>
-    <t>-5800|-2570|241</t>
+    <t>-79446.109375|81882.3125|-9.289999961853027</t>
   </si>
   <si>
     <t>5|5|1</t>
   </si>
   <si>
-    <t>-4000|-2600|241</t>
-  </si>
-  <si>
-    <t>14|4|1</t>
-  </si>
-  <si>
-    <t>-5124|-2342|241</t>
-  </si>
-  <si>
-    <t>8|2.5|1</t>
-  </si>
-  <si>
-    <t>-1060|-280|241</t>
-  </si>
-  <si>
-    <t>6|22|1</t>
-  </si>
-  <si>
-    <t>-2374|-2358|241</t>
-  </si>
-  <si>
-    <t>6|3|1</t>
-  </si>
-  <si>
-    <t>-1394|-1783|241</t>
-  </si>
-  <si>
-    <t>4|4|1</t>
-  </si>
-  <si>
-    <t>-1647|-624|241</t>
-  </si>
-  <si>
-    <t>-1652|966|241</t>
-  </si>
-  <si>
-    <t>5|4|1</t>
-  </si>
-  <si>
-    <t>-2899|1824|241</t>
-  </si>
-  <si>
-    <t>12|3.5|1</t>
-  </si>
-  <si>
-    <t>-2112|-60|241</t>
-  </si>
-  <si>
-    <t>2|40|1</t>
-  </si>
-  <si>
-    <t>-4465|2023|241</t>
-  </si>
-  <si>
-    <t>12|3|1</t>
-  </si>
-  <si>
-    <t>-6678|1872|241</t>
-  </si>
-  <si>
-    <t>-3319|-313|241</t>
-  </si>
-  <si>
-    <t>6|12|1</t>
-  </si>
-  <si>
-    <t>-3555|733|241</t>
-  </si>
-  <si>
-    <t>2|7|1</t>
-  </si>
-  <si>
-    <t>-4732|1014|241</t>
-  </si>
-  <si>
-    <t>4|3|1</t>
-  </si>
-  <si>
-    <t>-5688|1011|241</t>
-  </si>
-  <si>
-    <t>7|2|1</t>
-  </si>
-  <si>
-    <t>-3857|-1605|241</t>
-  </si>
-  <si>
-    <t>8|3|1</t>
-  </si>
-  <si>
-    <t>-5039|-1651|241</t>
-  </si>
-  <si>
-    <t>10|2|1</t>
-  </si>
-  <si>
-    <t>-6341|617|241</t>
-  </si>
-  <si>
-    <t>3|3|1</t>
-  </si>
-  <si>
-    <t>-6506|-141|241</t>
-  </si>
-  <si>
-    <t>5|3|1</t>
-  </si>
-  <si>
-    <t>-6175|-1585|241</t>
-  </si>
-  <si>
-    <t>-6499|-986|241</t>
+    <t>-80290.59375|84541.21875|-10.329999923706055</t>
+  </si>
+  <si>
+    <t>-79490.703125|83387.0625|-10.779999732971191</t>
+  </si>
+  <si>
+    <t>-76741.7890625|80767.09375|-9.489999771118164</t>
+  </si>
+  <si>
+    <t>-76103.953125|82022.4296875|-9.390000343322754</t>
+  </si>
+  <si>
+    <t>-76356.90625|82972.5078125|-10.779999732971191</t>
+  </si>
+  <si>
+    <t>-78609.140625|84421.09375|-10.779999732971191</t>
+  </si>
+  <si>
+    <t>-81470.2109375|82365.9921875|498.550048828125</t>
+  </si>
+  <si>
+    <t>-79255.1171875|80622.953125|-9.609999656677246</t>
+  </si>
+  <si>
+    <t>-79571.5625|80041.2421875|-10.119999885559082</t>
+  </si>
+  <si>
+    <t>-75396.09375|83219.703125|-10.779999732971191</t>
+  </si>
+  <si>
+    <t>-74638.9609375|82222.4765625|-9.289999961853027</t>
+  </si>
+  <si>
+    <t>-77157.15625|82015.6171875|-9.5</t>
+  </si>
+  <si>
+    <t>-79144.15625|85612.4375|-10.779999732971191</t>
+  </si>
+  <si>
+    <t>-78793.171875|83576.59375|-10.779999732971191</t>
+  </si>
+  <si>
+    <t>-78605.40625|81807.5078125|-9.289999961853027</t>
+  </si>
+  <si>
+    <t>-84672.796875|84138.2734375|515.9500122070312</t>
+  </si>
+  <si>
+    <t>-82966.09375|84092.1171875|515.9500122070312</t>
+  </si>
+  <si>
+    <t>-85546.15625|85221.4296875|498.54998779296875</t>
+  </si>
+  <si>
+    <t>-85206.421875|83149.78125|498.54998779296875</t>
+  </si>
+  <si>
+    <t>-84378.5234375|82555.3515625|498.54998779296875</t>
+  </si>
+  <si>
+    <t>-82397.34375|82851.140625|498.550048828125</t>
+  </si>
+  <si>
+    <t>-81604.78125|83680.0078125|498.54998779296875</t>
+  </si>
+  <si>
+    <t>-81404.09375|84625.1875|498.550048828125</t>
+  </si>
+  <si>
+    <t>-82204.7421875|85281.359375|498.54998779296875</t>
   </si>
   <si>
     <t>77831.6015625|77991.15625|287.6199951171875</t>
@@ -968,6 +908,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1362,7 +1305,7 @@
       <c r="A6">
         <v>10001</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
@@ -1380,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1391,10 +1334,10 @@
         <v>10003</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1405,13 +1348,10 @@
         <v>10004</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1" spans="1:4">
@@ -1419,13 +1359,10 @@
         <v>10005</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="23" customHeight="1" spans="1:4">
@@ -1433,13 +1370,10 @@
         <v>10006</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1" spans="1:4">
@@ -1447,13 +1381,10 @@
         <v>10007</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1" spans="1:4">
@@ -1461,13 +1392,10 @@
         <v>10008</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1" spans="1:4">
@@ -1475,13 +1403,10 @@
         <v>10009</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1" spans="1:4">
@@ -1489,13 +1414,10 @@
         <v>10010</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1" spans="1:4">
@@ -1503,13 +1425,10 @@
         <v>10011</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1" spans="1:4">
@@ -1517,13 +1436,10 @@
         <v>10012</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1" spans="1:4">
@@ -1531,13 +1447,10 @@
         <v>10013</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1" spans="1:4">
@@ -1545,134 +1458,131 @@
         <v>10014</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1" spans="1:4">
       <c r="A20">
         <v>10015</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1" spans="1:4">
       <c r="A21">
         <v>10016</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1" spans="1:4">
       <c r="A22">
         <v>10017</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1" spans="1:4">
       <c r="A23">
         <v>10018</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" ht="23" customHeight="1" spans="1:4">
       <c r="A24">
         <v>10019</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" ht="23" customHeight="1" spans="1:4">
       <c r="A25">
         <v>10020</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" ht="23" customHeight="1" spans="1:4">
       <c r="A26">
         <v>10021</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" ht="23" customHeight="1" spans="1:4">
       <c r="A27">
         <v>10022</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" ht="23" customHeight="1" spans="1:4">
       <c r="A28">
         <v>10023</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" ht="23" customHeight="1" spans="1:4">
       <c r="A29">
         <v>10024</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" ht="23" customHeight="1" spans="1:3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" ht="23" customHeight="1" spans="1:4">
       <c r="A30">
         <v>10025</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1" spans="1:4">
@@ -1694,10 +1604,10 @@
         <v>20001</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
@@ -1708,10 +1618,10 @@
         <v>20002</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -1722,10 +1632,10 @@
         <v>20003</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -1736,10 +1646,10 @@
         <v>20004</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -1750,10 +1660,10 @@
         <v>20005</v>
       </c>
       <c r="B36" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -1764,10 +1674,10 @@
         <v>20006</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -1778,10 +1688,10 @@
         <v>20007</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -1792,10 +1702,10 @@
         <v>20008</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -1806,10 +1716,10 @@
         <v>20009</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -1820,10 +1730,10 @@
         <v>20010</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -1834,10 +1744,10 @@
         <v>20011</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -1848,10 +1758,10 @@
         <v>20012</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1862,10 +1772,10 @@
         <v>20013</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -1876,101 +1786,101 @@
         <v>20014</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1" spans="1:3">
+    <row r="46" ht="24" customHeight="1" spans="1:4">
       <c r="A46">
         <v>20015</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" ht="24" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:4">
       <c r="A47">
         <v>20016</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="1:4">
       <c r="A48">
         <v>20017</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1" spans="1:4">
       <c r="A49">
         <v>20018</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1" spans="1:4">
       <c r="A50">
         <v>20019</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:4">
       <c r="A51">
         <v>20020</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" ht="24" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1" spans="1:4">
       <c r="A52">
         <v>20021</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="1:4">
       <c r="A53">
         <v>20022</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:4">
@@ -1992,10 +1902,10 @@
         <v>30001</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -2006,10 +1916,10 @@
         <v>30002</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -2020,10 +1930,10 @@
         <v>30003</v>
       </c>
       <c r="B57" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -2034,10 +1944,10 @@
         <v>30004</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -2048,10 +1958,10 @@
         <v>30005</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
@@ -2062,10 +1972,10 @@
         <v>30006</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
@@ -2076,10 +1986,10 @@
         <v>30007</v>
       </c>
       <c r="B61" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -2090,10 +2000,10 @@
         <v>30008</v>
       </c>
       <c r="B62" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s">
         <v>10</v>
@@ -2104,10 +2014,10 @@
         <v>30009</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D63" t="s">
         <v>10</v>
@@ -2118,10 +2028,10 @@
         <v>30010</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D64" t="s">
         <v>10</v>
@@ -2132,10 +2042,10 @@
         <v>30011</v>
       </c>
       <c r="B65" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
@@ -2146,10 +2056,10 @@
         <v>30012</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D66" t="s">
         <v>10</v>
@@ -2160,10 +2070,10 @@
         <v>30013</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D67" t="s">
         <v>10</v>
@@ -2174,102 +2084,102 @@
         <v>30014</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D68" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="69" ht="21" customHeight="1" spans="1:3">
+    <row r="69" ht="21" customHeight="1" spans="1:4">
       <c r="A69" s="2">
         <v>30015</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" ht="21" customHeight="1" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" ht="21" customHeight="1" spans="1:4">
       <c r="A70" s="2">
         <v>30016</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" s="2">
         <v>30017</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" s="2">
         <v>30018</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="2">
         <v>30019</v>
       </c>
       <c r="B73" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" s="2">
         <v>30020</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="2">
         <v>30021</v>
       </c>
       <c r="B75" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" s="2"/>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:4">
       <c r="A77" s="2"/>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:4">
       <c r="A78" s="2"/>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:4">
       <c r="A79" s="2"/>
     </row>
   </sheetData>
